--- a/data/trans_camb/P23_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 8,23</t>
+          <t>-7,76; 9,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 7,1</t>
+          <t>-9,97; 6,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,91; -1,37</t>
+          <t>-19,05; -2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 17,3</t>
+          <t>1,05; 16,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 8,0</t>
+          <t>-6,74; 7,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 3,57</t>
+          <t>-9,15; 4,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 10,64</t>
+          <t>-1,65; 10,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,72</t>
+          <t>-5,99; 4,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -1,84</t>
+          <t>-12,39; -1,37</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 23,97</t>
+          <t>-17,95; 27,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 21,59</t>
+          <t>-23,7; 18,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,55; -4,51</t>
+          <t>-46,62; -7,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 83,13</t>
+          <t>3,12; 80,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 37,13</t>
+          <t>-23,92; 38,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 16,68</t>
+          <t>-31,6; 21,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 36,33</t>
+          <t>-4,86; 35,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 16,49</t>
+          <t>-17,66; 16,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,37; -6,16</t>
+          <t>-35,68; -4,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,31</t>
+          <t>-3,75; 9,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 11,96</t>
+          <t>-2,32; 11,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -3,26</t>
+          <t>-16,74; -3,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 10,84</t>
+          <t>0,01; 10,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 10,03</t>
+          <t>-0,51; 10,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 1,67</t>
+          <t>-7,74; 1,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,71</t>
+          <t>-0,08; 8,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,21</t>
+          <t>0,67; 9,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -2,42</t>
+          <t>-10,41; -1,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 31,98</t>
+          <t>-9,42; 30,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 36,47</t>
+          <t>-5,77; 34,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,65; -10,17</t>
+          <t>-43,41; -9,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 53,85</t>
+          <t>0,09; 55,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 49,76</t>
+          <t>-2,45; 54,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 8,41</t>
+          <t>-31,96; 8,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 31,87</t>
+          <t>-0,37; 30,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 34,44</t>
+          <t>2,05; 35,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,15; -8,74</t>
+          <t>-33,6; -6,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 3,03</t>
+          <t>-12,5; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,51; -5,74</t>
+          <t>-19,97; -4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,4; -11,7</t>
+          <t>-26,28; -11,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 4,21</t>
+          <t>-9,42; 4,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 3,03</t>
+          <t>-11,09; 2,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -3,21</t>
+          <t>-15,38; -4,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 1,98</t>
+          <t>-8,94; 1,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -3,2</t>
+          <t>-12,87; -2,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,02; -10,01</t>
+          <t>-18,85; -9,84</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 7,74</t>
+          <t>-26,48; 9,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,82; -14,72</t>
+          <t>-42,71; -11,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,63; -31,11</t>
+          <t>-57,37; -30,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 17,15</t>
+          <t>-29,55; 19,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 12,78</t>
+          <t>-35,74; 11,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -12,8</t>
+          <t>-49,29; -16,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 5,88</t>
+          <t>-23,45; 5,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -9,84</t>
+          <t>-34,19; -9,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,9; -29,98</t>
+          <t>-50,14; -29,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,52; -6,57</t>
+          <t>-20,78; -6,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 0,37</t>
+          <t>-14,37; -0,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,14; -12,12</t>
+          <t>-28,76; -12,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 5,95</t>
+          <t>-6,77; 6,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 8,61</t>
+          <t>-4,72; 7,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,51; -4,95</t>
+          <t>-18,62; -4,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -2,49</t>
+          <t>-11,38; -1,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,8</t>
+          <t>-7,6; 2,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -10,8</t>
+          <t>-22,93; -11,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,09; -15,89</t>
+          <t>-42,9; -15,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 1,38</t>
+          <t>-29,69; 0,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,35; -27,86</t>
+          <t>-59,61; -29,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 24,75</t>
+          <t>-22,66; 27,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 37,48</t>
+          <t>-15,65; 34,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,07; -19,7</t>
+          <t>-64,69; -18,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,36; -7,6</t>
+          <t>-30,05; -4,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 5,35</t>
+          <t>-20,07; 7,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,85; -32,22</t>
+          <t>-61,9; -34,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 13,79</t>
+          <t>-7,22; 12,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 11,66</t>
+          <t>-9,07; 10,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,52; -10,71</t>
+          <t>-28,0; -11,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 12,19</t>
+          <t>-6,43; 11,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 7,42</t>
+          <t>-9,35; 6,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,95; -5,69</t>
+          <t>-20,48; -5,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 9,45</t>
+          <t>-3,72; 8,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 6,15</t>
+          <t>-6,41; 6,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -11,14</t>
+          <t>-22,14; -10,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 41,88</t>
+          <t>-16,78; 37,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 32,65</t>
+          <t>-20,82; 29,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,84; -31,22</t>
+          <t>-62,87; -32,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 54,98</t>
+          <t>-20,23; 50,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 34,86</t>
+          <t>-29,33; 29,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,15; -26,07</t>
+          <t>-62,42; -25,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 32,85</t>
+          <t>-10,34; 29,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 21,17</t>
+          <t>-17,87; 22,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-60,41; -37,12</t>
+          <t>-60,33; -36,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,21; -6,88</t>
+          <t>-23,72; -6,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -3,59</t>
+          <t>-20,44; -3,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,34; -9,24</t>
+          <t>-25,76; -10,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 8,45</t>
+          <t>-5,71; 8,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 10,79</t>
+          <t>-2,99; 11,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 2,02</t>
+          <t>-10,11; 2,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,2; -1,75</t>
+          <t>-12,44; -1,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 2,15</t>
+          <t>-9,52; 1,67</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -5,88</t>
+          <t>-16,16; -5,62</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,53; -16,12</t>
+          <t>-48,01; -16,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,37; -8,36</t>
+          <t>-41,08; -8,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-50,82; -22,45</t>
+          <t>-51,37; -23,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 43,18</t>
+          <t>-21,82; 43,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 57,64</t>
+          <t>-11,78; 56,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 11,08</t>
+          <t>-37,56; 16,88</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -5,81</t>
+          <t>-34,22; -5,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 7,07</t>
+          <t>-26,11; 4,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-42,0; -18,12</t>
+          <t>-43,45; -17,7</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 7,89</t>
+          <t>-4,28; 7,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -1,25</t>
+          <t>-12,0; -1,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,53; -2,99</t>
+          <t>-14,64; -2,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 6,93</t>
+          <t>-2,81; 7,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 4,32</t>
+          <t>-4,79; 5,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 0,09</t>
+          <t>-19,62; -0,33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,62</t>
+          <t>-1,65; 5,83</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 0,25</t>
+          <t>-7,03; -0,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -4,18</t>
+          <t>-18,56; -3,56</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 23,21</t>
+          <t>-11,04; 20,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,2; -3,71</t>
+          <t>-30,58; -3,5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,93; -8,28</t>
+          <t>-37,13; -7,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 30,02</t>
+          <t>-9,81; 32,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 18,2</t>
+          <t>-17,58; 23,16</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 0,03</t>
+          <t>-66,54; -1,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 19,12</t>
+          <t>-4,78; 20,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 0,84</t>
+          <t>-21,57; -0,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-55,48; -14,37</t>
+          <t>-55,63; -12,15</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 1,02</t>
+          <t>-9,5; 0,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -2,08</t>
+          <t>-12,54; -2,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -11,31</t>
+          <t>-31,73; -11,06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 6,6</t>
+          <t>-1,37; 6,92</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 7,26</t>
+          <t>-1,14; 7,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -2,35</t>
+          <t>-9,78; -2,46</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,65</t>
+          <t>-4,04; 2,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,4</t>
+          <t>-5,21; 1,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-20,63; -8,59</t>
+          <t>-21,32; -8,47</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 2,99</t>
+          <t>-22,52; 2,03</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-28,12; -5,47</t>
+          <t>-29,04; -5,22</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-77,26; -29,13</t>
+          <t>-75,47; -28,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 32,46</t>
+          <t>-5,97; 32,93</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 34,87</t>
+          <t>-4,6; 36,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,3; -10,9</t>
+          <t>-38,99; -11,01</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 9,03</t>
+          <t>-12,25; 8,76</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 4,64</t>
+          <t>-15,91; 5,16</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-63,31; -28,26</t>
+          <t>-64,37; -27,92</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,41</t>
+          <t>-5,63; -0,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -2,75</t>
+          <t>-7,55; -2,72</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -12,54</t>
+          <t>-21,58; -12,99</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,62</t>
+          <t>0,3; 4,59</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,6</t>
+          <t>-0,64; 3,64</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -4,56</t>
+          <t>-10,26; -4,42</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,38</t>
+          <t>-1,8; 1,34</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,25</t>
+          <t>-3,34; -0,16</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -9,13</t>
+          <t>-14,18; -9,24</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -1,18</t>
+          <t>-13,55; -1,86</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -7,1</t>
+          <t>-18,27; -7,06</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-52,11; -32,38</t>
+          <t>-53,17; -33,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,15; 19,73</t>
+          <t>1,3; 19,98</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 15,5</t>
+          <t>-2,5; 15,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-40,53; -19,35</t>
+          <t>-40,45; -18,68</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 4,46</t>
+          <t>-5,51; 4,3</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,86</t>
+          <t>-10,13; -0,49</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-43,5; -29,02</t>
+          <t>-43,95; -29,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P23_R2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,98</t>
+          <t>-14,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-4,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,82</t>
+          <t>-9,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 9,37</t>
+          <t>-7,6; 8,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 6,24</t>
+          <t>-10,34; 6,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -2,59</t>
+          <t>-21,97; -6,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 16,64</t>
+          <t>0,46; 16,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 7,88</t>
+          <t>-6,35; 8,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 4,41</t>
+          <t>-11,0; 2,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 10,21</t>
+          <t>-1,5; 10,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 4,7</t>
+          <t>-6,06; 5,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -1,37</t>
+          <t>-14,46; -4,29</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-28,84%</t>
+          <t>-37,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,14%</t>
+          <t>-16,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-21,53%</t>
+          <t>-29,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 27,4</t>
+          <t>-18,07; 24,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 18,22</t>
+          <t>-24,25; 18,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,62; -7,65</t>
+          <t>-51,89; -17,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 80,81</t>
+          <t>2,22; 79,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 38,62</t>
+          <t>-21,9; 38,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 21,12</t>
+          <t>-37,07; 9,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 35,66</t>
+          <t>-5,03; 36,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 16,21</t>
+          <t>-17,41; 17,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,68; -4,13</t>
+          <t>-41,37; -14,96</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,12</t>
+          <t>-10,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-3,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-6,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 9,83</t>
+          <t>-2,59; 10,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 11,45</t>
+          <t>-0,42; 12,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,74; -3,14</t>
+          <t>-16,96; -3,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 10,6</t>
+          <t>0,03; 10,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 10,38</t>
+          <t>-0,36; 9,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 1,89</t>
+          <t>-8,12; 1,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 8,34</t>
+          <t>-0,57; 8,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 9,66</t>
+          <t>0,85; 9,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -1,83</t>
+          <t>-10,87; -2,86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-28,18%</t>
+          <t>-28,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,39%</t>
+          <t>-15,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,25%</t>
+          <t>-23,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 30,45</t>
+          <t>-6,7; 30,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 34,96</t>
+          <t>-1,35; 39,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -9,03</t>
+          <t>-43,83; -10,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 55,56</t>
+          <t>0,06; 52,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 54,36</t>
+          <t>-1,56; 50,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 8,89</t>
+          <t>-32,93; 6,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 30,68</t>
+          <t>-1,84; 31,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 35,48</t>
+          <t>2,62; 35,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,6; -6,82</t>
+          <t>-35,23; -10,66</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-19,48</t>
+          <t>-17,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,62</t>
+          <t>-9,88</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,49</t>
+          <t>-13,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 3,78</t>
+          <t>-12,26; 3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,97; -4,3</t>
+          <t>-20,55; -5,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,28; -11,53</t>
+          <t>-25,02; -9,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 4,95</t>
+          <t>-10,25; 3,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 2,71</t>
+          <t>-10,41; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -4,03</t>
+          <t>-15,59; -4,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 1,72</t>
+          <t>-8,65; 1,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -2,84</t>
+          <t>-13,05; -3,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,85; -9,84</t>
+          <t>-18,54; -9,08</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-45,35%</t>
+          <t>-41,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-34,33%</t>
+          <t>-35,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,04%</t>
+          <t>-39,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 9,65</t>
+          <t>-25,73; 9,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,71; -11,78</t>
+          <t>-43,64; -14,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -30,23</t>
+          <t>-53,44; -25,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 19,93</t>
+          <t>-32,73; 16,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 11,47</t>
+          <t>-33,71; 14,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,29; -16,42</t>
+          <t>-49,85; -16,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 5,02</t>
+          <t>-22,5; 5,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,19; -9,07</t>
+          <t>-35,13; -9,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,14; -29,74</t>
+          <t>-48,8; -27,69</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-20,53</t>
+          <t>-20,22</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,05</t>
+          <t>-7,5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-16,56</t>
+          <t>-13,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,78; -6,22</t>
+          <t>-21,09; -7,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -0,08</t>
+          <t>-14,49; 0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,76; -12,21</t>
+          <t>-28,05; -12,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 6,26</t>
+          <t>-6,8; 6,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 7,93</t>
+          <t>-4,62; 8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,62; -4,49</t>
+          <t>-13,32; -1,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -1,6</t>
+          <t>-12,17; -2,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,39</t>
+          <t>-7,74; 2,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,93; -11,57</t>
+          <t>-18,88; -8,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-45,58%</t>
+          <t>-44,91%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-41,66%</t>
+          <t>-28,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,5%</t>
+          <t>-38,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,9; -15,25</t>
+          <t>-43,48; -17,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 0,02</t>
+          <t>-30,34; 0,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,61; -29,09</t>
+          <t>-57,8; -27,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 27,75</t>
+          <t>-23,47; 28,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 34,06</t>
+          <t>-15,3; 36,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,69; -18,54</t>
+          <t>-44,89; -5,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,05; -4,32</t>
+          <t>-31,7; -7,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 7,11</t>
+          <t>-21,08; 6,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -34,26</t>
+          <t>-50,16; -26,65</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-19,74</t>
+          <t>-18,63</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-12,92</t>
+          <t>-13,07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-16,45</t>
+          <t>-15,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 12,68</t>
+          <t>-7,8; 12,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 10,21</t>
+          <t>-7,74; 11,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,0; -11,32</t>
+          <t>-27,25; -10,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 11,27</t>
+          <t>-6,12; 11,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 6,51</t>
+          <t>-10,09; 6,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,48; -5,92</t>
+          <t>-19,64; -5,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 8,94</t>
+          <t>-3,75; 9,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 6,75</t>
+          <t>-5,67; 7,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -10,65</t>
+          <t>-21,16; -10,88</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-51,1%</t>
+          <t>-48,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-47,46%</t>
+          <t>-48,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-50,04%</t>
+          <t>-48,49%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 37,03</t>
+          <t>-17,66; 39,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 29,61</t>
+          <t>-17,99; 31,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,87; -32,56</t>
+          <t>-62,34; -31,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 50,9</t>
+          <t>-21,17; 52,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 29,93</t>
+          <t>-30,84; 28,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,42; -25,23</t>
+          <t>-61,75; -25,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 29,64</t>
+          <t>-10,23; 31,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 22,03</t>
+          <t>-15,87; 25,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-60,33; -36,25</t>
+          <t>-57,44; -36,03</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-17,73</t>
+          <t>-17,5</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-4,16</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-10,6</t>
+          <t>-10,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -6,8</t>
+          <t>-24,0; -7,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,44; -3,15</t>
+          <t>-20,13; -4,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,76; -10,1</t>
+          <t>-25,67; -9,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 8,24</t>
+          <t>-6,69; 7,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 11,03</t>
+          <t>-2,77; 11,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 2,97</t>
+          <t>-10,85; 1,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -1,74</t>
+          <t>-12,51; -1,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 1,67</t>
+          <t>-9,51; 1,71</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -5,62</t>
+          <t>-15,87; -6,05</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-38,91%</t>
+          <t>-38,41%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-17,57%</t>
+          <t>-18,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-31,19%</t>
+          <t>-31,24%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -16,5</t>
+          <t>-48,59; -17,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -8,02</t>
+          <t>-41,04; -10,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,37; -23,66</t>
+          <t>-51,04; -23,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 43,57</t>
+          <t>-24,47; 40,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 56,25</t>
+          <t>-10,05; 60,89</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 16,88</t>
+          <t>-39,5; 9,9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -5,49</t>
+          <t>-34,11; -4,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 4,53</t>
+          <t>-25,92; 5,57</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,45; -17,7</t>
+          <t>-42,58; -18,35</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-9,25</t>
+          <t>-10,51</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-7,27</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-8,89</t>
+          <t>-6,37</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 7,05</t>
+          <t>-3,59; 7,31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,0; -1,2</t>
+          <t>-12,75; -1,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,64; -2,81</t>
+          <t>-15,67; -4,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 7,28</t>
+          <t>-2,89; 7,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 5,09</t>
+          <t>-4,75; 4,81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -0,33</t>
+          <t>-6,55; 2,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 5,83</t>
+          <t>-2,27; 5,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -0,05</t>
+          <t>-7,22; 0,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,56; -3,56</t>
+          <t>-9,66; -2,79</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-24,99%</t>
+          <t>-28,39%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-28,78%</t>
+          <t>-9,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-28,65%</t>
+          <t>-20,51%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 20,06</t>
+          <t>-8,95; 21,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-30,58; -3,5</t>
+          <t>-32,0; -4,78</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,13; -7,81</t>
+          <t>-39,76; -13,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 32,07</t>
+          <t>-10,05; 32,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 23,16</t>
+          <t>-17,03; 21,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-66,54; -1,31</t>
+          <t>-23,09; 10,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 20,35</t>
+          <t>-6,82; 18,7</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -0,2</t>
+          <t>-21,91; 0,37</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-55,63; -12,15</t>
+          <t>-29,51; -9,54</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-20,05</t>
+          <t>-13,57</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-6,17</t>
+          <t>-6,49</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-12,68</t>
+          <t>-9,91</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,73</t>
+          <t>-9,07; 0,88</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -2,13</t>
+          <t>-12,14; -2,03</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-31,73; -11,06</t>
+          <t>-18,94; -8,47</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 6,92</t>
+          <t>-2,3; 6,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 7,4</t>
+          <t>-1,17; 7,65</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-9,78; -2,46</t>
+          <t>-10,28; -2,56</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,59</t>
+          <t>-3,98; 2,76</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 1,52</t>
+          <t>-5,68; 1,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -8,47</t>
+          <t>-13,2; -6,63</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-50,3%</t>
+          <t>-34,02%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-27,09%</t>
+          <t>-28,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-40,79%</t>
+          <t>-31,88%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 2,03</t>
+          <t>-21,41; 2,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,04; -5,22</t>
+          <t>-28,61; -5,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-75,47; -28,72</t>
+          <t>-44,49; -22,52</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 32,93</t>
+          <t>-9,39; 31,56</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 36,13</t>
+          <t>-4,88; 37,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-38,99; -11,01</t>
+          <t>-40,99; -12,89</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 8,76</t>
+          <t>-12,42; 9,38</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 5,16</t>
+          <t>-17,1; 4,47</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-64,37; -27,92</t>
+          <t>-40,23; -22,34</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-15,71</t>
+          <t>-14,3</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-6,73</t>
+          <t>-5,6</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-11,19</t>
+          <t>-9,92</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,73</t>
+          <t>-5,54; -0,83</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -2,72</t>
+          <t>-7,56; -2,86</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-21,58; -12,99</t>
+          <t>-16,54; -11,85</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,59</t>
+          <t>0,08; 4,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,64</t>
+          <t>-0,5; 3,66</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -4,42</t>
+          <t>-7,36; -3,7</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,34</t>
+          <t>-1,9; 1,31</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,16</t>
+          <t>-3,48; -0,19</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -9,24</t>
+          <t>-11,4; -8,49</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-39,43%</t>
+          <t>-35,88%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-27,43%</t>
+          <t>-22,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-34,89%</t>
+          <t>-30,93%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -1,86</t>
+          <t>-13,46; -2,18</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -7,06</t>
+          <t>-18,49; -7,39</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -33,01</t>
+          <t>-40,67; -30,76</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,3; 19,98</t>
+          <t>0,3; 18,97</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 15,3</t>
+          <t>-1,88; 15,9</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-40,45; -18,68</t>
+          <t>-28,96; -15,76</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,3</t>
+          <t>-5,79; 4,12</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -0,49</t>
+          <t>-10,52; -0,56</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-43,95; -29,2</t>
+          <t>-34,75; -26,99</t>
         </is>
       </c>
     </row>
